--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2672"/>
+  <dimension ref="A1:E2673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72560,6 +72560,33 @@
         </is>
       </c>
     </row>
+    <row r="2673">
+      <c r="A2673" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B2673" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2673" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D2673" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E2673" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2673"/>
+  <dimension ref="A1:E2674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72587,6 +72587,33 @@
         </is>
       </c>
     </row>
+    <row r="2674">
+      <c r="A2674" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B2674" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2674" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D2674" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E2674" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2674"/>
+  <dimension ref="A1:E2675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72614,6 +72614,33 @@
         </is>
       </c>
     </row>
+    <row r="2675">
+      <c r="A2675" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2675" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2675" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D2675" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E2675" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2675"/>
+  <dimension ref="A1:E2676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72641,6 +72641,33 @@
         </is>
       </c>
     </row>
+    <row r="2676">
+      <c r="A2676" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2676" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2676" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D2676" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2676" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2676"/>
+  <dimension ref="A1:E2677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72668,6 +72668,33 @@
         </is>
       </c>
     </row>
+    <row r="2677">
+      <c r="A2677" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2677" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2677" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D2677" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E2677" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2677"/>
+  <dimension ref="A1:E2678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72695,6 +72695,33 @@
         </is>
       </c>
     </row>
+    <row r="2678">
+      <c r="A2678" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2678" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2678" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D2678" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E2678" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="history" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,31 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2678"/>
+  <dimension ref="A1:E2679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sorteo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>primero</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>segundo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tercero</t>
         </is>
@@ -72719,6 +72731,33 @@
       <c r="E2678" t="inlineStr">
         <is>
           <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2679">
+      <c r="A2679" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2679" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2679" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D2679" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E2679" t="inlineStr">
+        <is>
+          <t>57</t>
         </is>
       </c>
     </row>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2679"/>
+  <dimension ref="A1:E2680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72761,6 +72761,33 @@
         </is>
       </c>
     </row>
+    <row r="2680">
+      <c r="A2680" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2680" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2680" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D2680" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E2680" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2680"/>
+  <dimension ref="A1:E2681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72788,6 +72788,33 @@
         </is>
       </c>
     </row>
+    <row r="2681">
+      <c r="A2681" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2681" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2681" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D2681" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E2681" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2681"/>
+  <dimension ref="A1:E2682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72815,6 +72815,33 @@
         </is>
       </c>
     </row>
+    <row r="2682">
+      <c r="A2682" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2682" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2682" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D2682" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E2682" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2682"/>
+  <dimension ref="A1:E2683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72842,6 +72842,33 @@
         </is>
       </c>
     </row>
+    <row r="2683">
+      <c r="A2683" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2683" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2683" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D2683" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E2683" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2683"/>
+  <dimension ref="A1:E2684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72869,6 +72869,33 @@
         </is>
       </c>
     </row>
+    <row r="2684">
+      <c r="A2684" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2684" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2684" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D2684" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E2684" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2684"/>
+  <dimension ref="A1:E2685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72896,6 +72896,33 @@
         </is>
       </c>
     </row>
+    <row r="2685">
+      <c r="A2685" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B2685" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2685" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D2685" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E2685" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2685"/>
+  <dimension ref="A1:E2686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72923,6 +72923,33 @@
         </is>
       </c>
     </row>
+    <row r="2686">
+      <c r="A2686" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B2686" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2686" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D2686" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E2686" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2686"/>
+  <dimension ref="A1:E2687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72950,6 +72950,33 @@
         </is>
       </c>
     </row>
+    <row r="2687">
+      <c r="A2687" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B2687" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2687" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D2687" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E2687" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2687"/>
+  <dimension ref="A1:E2688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72977,6 +72977,33 @@
         </is>
       </c>
     </row>
+    <row r="2688">
+      <c r="A2688" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B2688" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2688" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D2688" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E2688" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2688"/>
+  <dimension ref="A1:E2689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73004,6 +73004,33 @@
         </is>
       </c>
     </row>
+    <row r="2689">
+      <c r="A2689" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2689" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2689" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D2689" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E2689" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2689"/>
+  <dimension ref="A1:E2690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73031,6 +73031,33 @@
         </is>
       </c>
     </row>
+    <row r="2690">
+      <c r="A2690" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2690" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2690" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D2690" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E2690" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2690"/>
+  <dimension ref="A1:E2691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73058,6 +73058,33 @@
         </is>
       </c>
     </row>
+    <row r="2691">
+      <c r="A2691" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2691" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2691" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D2691" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E2691" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2691"/>
+  <dimension ref="A1:E2692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73085,6 +73085,33 @@
         </is>
       </c>
     </row>
+    <row r="2692">
+      <c r="A2692" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2692" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2692" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D2692" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E2692" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2692"/>
+  <dimension ref="A1:E2693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73112,6 +73112,33 @@
         </is>
       </c>
     </row>
+    <row r="2693">
+      <c r="A2693" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2693" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2693" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D2693" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E2693" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2693"/>
+  <dimension ref="A1:E2694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73139,6 +73139,33 @@
         </is>
       </c>
     </row>
+    <row r="2694">
+      <c r="A2694" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2694" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2694" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D2694" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E2694" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2694"/>
+  <dimension ref="A1:E2695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73166,6 +73166,33 @@
         </is>
       </c>
     </row>
+    <row r="2695">
+      <c r="A2695" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B2695" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2695" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D2695" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E2695" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2695"/>
+  <dimension ref="A1:E2696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73193,6 +73193,33 @@
         </is>
       </c>
     </row>
+    <row r="2696">
+      <c r="A2696" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B2696" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2696" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D2696" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E2696" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2696"/>
+  <dimension ref="A1:E2697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73220,6 +73220,33 @@
         </is>
       </c>
     </row>
+    <row r="2697">
+      <c r="A2697" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2697" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2697" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D2697" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E2697" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2697"/>
+  <dimension ref="A1:E2698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73247,6 +73247,33 @@
         </is>
       </c>
     </row>
+    <row r="2698">
+      <c r="A2698" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2698" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2698" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D2698" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E2698" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2698"/>
+  <dimension ref="A1:E2699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73274,6 +73274,33 @@
         </is>
       </c>
     </row>
+    <row r="2699">
+      <c r="A2699" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B2699" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2699" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D2699" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E2699" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2699"/>
+  <dimension ref="A1:E2700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73301,6 +73301,33 @@
         </is>
       </c>
     </row>
+    <row r="2700">
+      <c r="A2700" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B2700" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2700" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D2700" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E2700" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2700"/>
+  <dimension ref="A1:E2701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73328,6 +73328,33 @@
         </is>
       </c>
     </row>
+    <row r="2701">
+      <c r="A2701" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B2701" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2701" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D2701" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E2701" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2701"/>
+  <dimension ref="A1:E2702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73355,6 +73355,33 @@
         </is>
       </c>
     </row>
+    <row r="2702">
+      <c r="A2702" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B2702" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2702" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D2702" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E2702" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2702"/>
+  <dimension ref="A1:E2703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73382,6 +73382,33 @@
         </is>
       </c>
     </row>
+    <row r="2703">
+      <c r="A2703" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B2703" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2703" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D2703" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E2703" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2703"/>
+  <dimension ref="A1:E2704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73409,6 +73409,33 @@
         </is>
       </c>
     </row>
+    <row r="2704">
+      <c r="A2704" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B2704" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2704" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D2704" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E2704" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2704"/>
+  <dimension ref="A1:E2705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73436,6 +73436,33 @@
         </is>
       </c>
     </row>
+    <row r="2705">
+      <c r="A2705" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2705" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2705" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D2705" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E2705" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2705"/>
+  <dimension ref="A1:E2706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73463,6 +73463,33 @@
         </is>
       </c>
     </row>
+    <row r="2706">
+      <c r="A2706" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2706" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2706" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D2706" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E2706" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2706"/>
+  <dimension ref="A1:E2707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73490,6 +73490,33 @@
         </is>
       </c>
     </row>
+    <row r="2707">
+      <c r="A2707" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2707" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2707" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D2707" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E2707" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2707"/>
+  <dimension ref="A1:E2708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73517,6 +73517,33 @@
         </is>
       </c>
     </row>
+    <row r="2708">
+      <c r="A2708" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2708" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2708" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D2708" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E2708" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2708"/>
+  <dimension ref="A1:E2709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73544,6 +73544,33 @@
         </is>
       </c>
     </row>
+    <row r="2709">
+      <c r="A2709" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2709" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2709" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D2709" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E2709" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2709"/>
+  <dimension ref="A1:E2710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73571,6 +73571,33 @@
         </is>
       </c>
     </row>
+    <row r="2710">
+      <c r="A2710" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2710" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2710" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D2710" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E2710" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2710"/>
+  <dimension ref="A1:E2711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73598,6 +73598,33 @@
         </is>
       </c>
     </row>
+    <row r="2711">
+      <c r="A2711" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B2711" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2711" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D2711" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E2711" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2711"/>
+  <dimension ref="A1:E2712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73625,6 +73625,33 @@
         </is>
       </c>
     </row>
+    <row r="2712">
+      <c r="A2712" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B2712" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2712" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D2712" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2712" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2712"/>
+  <dimension ref="A1:E2713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73652,6 +73652,33 @@
         </is>
       </c>
     </row>
+    <row r="2713">
+      <c r="A2713" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2713" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2713" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D2713" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E2713" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2713"/>
+  <dimension ref="A1:E2714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73679,6 +73679,33 @@
         </is>
       </c>
     </row>
+    <row r="2714">
+      <c r="A2714" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2714" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2714" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D2714" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E2714" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2714"/>
+  <dimension ref="A1:E2715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73706,6 +73706,33 @@
         </is>
       </c>
     </row>
+    <row r="2715">
+      <c r="A2715" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B2715" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2715" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D2715" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E2715" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2715"/>
+  <dimension ref="A1:E2716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73733,6 +73733,33 @@
         </is>
       </c>
     </row>
+    <row r="2716">
+      <c r="A2716" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B2716" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2716" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D2716" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E2716" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2716"/>
+  <dimension ref="A1:E2717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73760,6 +73760,33 @@
         </is>
       </c>
     </row>
+    <row r="2717">
+      <c r="A2717" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B2717" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2717" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D2717" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E2717" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2717"/>
+  <dimension ref="A1:E2718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73787,6 +73787,33 @@
         </is>
       </c>
     </row>
+    <row r="2718">
+      <c r="A2718" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B2718" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2718" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D2718" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E2718" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2718"/>
+  <dimension ref="A1:E2719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73814,6 +73814,33 @@
         </is>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2719" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2719" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D2719" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E2719" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2719"/>
+  <dimension ref="A1:E2720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73841,6 +73841,33 @@
         </is>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2720" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2720" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D2720" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E2720" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2720"/>
+  <dimension ref="A1:E2721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73868,6 +73868,33 @@
         </is>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2721" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2721" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D2721" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E2721" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2721"/>
+  <dimension ref="A1:E2722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73895,6 +73895,33 @@
         </is>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2722" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2722" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D2722" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E2722" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2722"/>
+  <dimension ref="A1:E2723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73922,6 +73922,33 @@
         </is>
       </c>
     </row>
+    <row r="2723">
+      <c r="A2723" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B2723" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2723" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D2723" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E2723" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2723"/>
+  <dimension ref="A1:E2724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73949,6 +73949,33 @@
         </is>
       </c>
     </row>
+    <row r="2724">
+      <c r="A2724" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B2724" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2724" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D2724" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E2724" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2724"/>
+  <dimension ref="A1:E2725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73976,6 +73976,33 @@
         </is>
       </c>
     </row>
+    <row r="2725">
+      <c r="A2725" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B2725" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2725" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D2725" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E2725" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2725"/>
+  <dimension ref="A1:E2726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74003,6 +74003,33 @@
         </is>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B2726" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2726" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D2726" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E2726" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2726"/>
+  <dimension ref="A1:E2727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74030,6 +74030,33 @@
         </is>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2727" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2727" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D2727" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E2727" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2727"/>
+  <dimension ref="A1:E2728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74057,6 +74057,33 @@
         </is>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2728" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2728" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D2728" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E2728" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2728"/>
+  <dimension ref="A1:E2729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74084,6 +74084,33 @@
         </is>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B2729" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2729" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D2729" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E2729" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2729"/>
+  <dimension ref="A1:E2730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74111,6 +74111,33 @@
         </is>
       </c>
     </row>
+    <row r="2730">
+      <c r="A2730" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B2730" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2730" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D2730" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E2730" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2730"/>
+  <dimension ref="A1:E2731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74138,6 +74138,33 @@
         </is>
       </c>
     </row>
+    <row r="2731">
+      <c r="A2731" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2731" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2731" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D2731" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E2731" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2731"/>
+  <dimension ref="A1:E2732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74165,6 +74165,33 @@
         </is>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2732" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2732" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D2732" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E2732" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2732"/>
+  <dimension ref="A1:E2733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74192,6 +74192,33 @@
         </is>
       </c>
     </row>
+    <row r="2733">
+      <c r="A2733" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2733" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2733" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D2733" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E2733" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2733"/>
+  <dimension ref="A1:E2734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74219,6 +74219,33 @@
         </is>
       </c>
     </row>
+    <row r="2734">
+      <c r="A2734" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2734" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2734" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D2734" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E2734" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2734"/>
+  <dimension ref="A1:E2735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74246,6 +74246,33 @@
         </is>
       </c>
     </row>
+    <row r="2735">
+      <c r="A2735" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2735" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2735" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D2735" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E2735" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2735"/>
+  <dimension ref="A1:E2736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74273,6 +74273,33 @@
         </is>
       </c>
     </row>
+    <row r="2736">
+      <c r="A2736" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2736" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2736" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D2736" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E2736" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2736"/>
+  <dimension ref="A1:E2737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74300,6 +74300,33 @@
         </is>
       </c>
     </row>
+    <row r="2737">
+      <c r="A2737" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2737" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2737" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D2737" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E2737" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2737"/>
+  <dimension ref="A1:E2738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74327,6 +74327,33 @@
         </is>
       </c>
     </row>
+    <row r="2738">
+      <c r="A2738" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2738" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2738" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D2738" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E2738" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2738"/>
+  <dimension ref="A1:E2739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74354,6 +74354,33 @@
         </is>
       </c>
     </row>
+    <row r="2739">
+      <c r="A2739" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2739" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2739" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D2739" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E2739" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2739"/>
+  <dimension ref="A1:E2740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74381,6 +74381,33 @@
         </is>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2740" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2740" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D2740" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E2740" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2740"/>
+  <dimension ref="A1:E2741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74408,6 +74408,33 @@
         </is>
       </c>
     </row>
+    <row r="2741">
+      <c r="A2741" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B2741" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2741" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D2741" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E2741" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2741"/>
+  <dimension ref="A1:E2742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74435,6 +74435,33 @@
         </is>
       </c>
     </row>
+    <row r="2742">
+      <c r="A2742" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B2742" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2742" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D2742" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E2742" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2742"/>
+  <dimension ref="A1:E2743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74462,6 +74462,33 @@
         </is>
       </c>
     </row>
+    <row r="2743">
+      <c r="A2743" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B2743" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2743" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D2743" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E2743" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2743"/>
+  <dimension ref="A1:E2744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74489,6 +74489,33 @@
         </is>
       </c>
     </row>
+    <row r="2744">
+      <c r="A2744" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B2744" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2744" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D2744" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E2744" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2744"/>
+  <dimension ref="A1:E2745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74516,6 +74516,33 @@
         </is>
       </c>
     </row>
+    <row r="2745">
+      <c r="A2745" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2745" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2745" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D2745" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E2745" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2745"/>
+  <dimension ref="A1:E2746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74543,6 +74543,33 @@
         </is>
       </c>
     </row>
+    <row r="2746">
+      <c r="A2746" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2746" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2746" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D2746" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E2746" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2746"/>
+  <dimension ref="A1:E2747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74570,6 +74570,33 @@
         </is>
       </c>
     </row>
+    <row r="2747">
+      <c r="A2747" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2747" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2747" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D2747" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E2747" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2747"/>
+  <dimension ref="A1:E2748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74597,6 +74597,33 @@
         </is>
       </c>
     </row>
+    <row r="2748">
+      <c r="A2748" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2748" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2748" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D2748" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E2748" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2748"/>
+  <dimension ref="A1:E2749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74624,6 +74624,33 @@
         </is>
       </c>
     </row>
+    <row r="2749">
+      <c r="A2749" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2749" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2749" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D2749" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E2749" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2749"/>
+  <dimension ref="A1:E2750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74651,6 +74651,33 @@
         </is>
       </c>
     </row>
+    <row r="2750">
+      <c r="A2750" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2750" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2750" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D2750" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E2750" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2750"/>
+  <dimension ref="A1:E2751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74678,6 +74678,33 @@
         </is>
       </c>
     </row>
+    <row r="2751">
+      <c r="A2751" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2751" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2751" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D2751" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E2751" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2751"/>
+  <dimension ref="A1:E2752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74705,6 +74705,33 @@
         </is>
       </c>
     </row>
+    <row r="2752">
+      <c r="A2752" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2752" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2752" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D2752" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E2752" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2752"/>
+  <dimension ref="A1:E2753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74732,6 +74732,33 @@
         </is>
       </c>
     </row>
+    <row r="2753">
+      <c r="A2753" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2753" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2753" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D2753" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E2753" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2753"/>
+  <dimension ref="A1:E2755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74759,6 +74759,60 @@
         </is>
       </c>
     </row>
+    <row r="2754">
+      <c r="A2754" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2754" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2754" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D2754" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E2754" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="2755">
+      <c r="A2755" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B2755" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2755" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D2755" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E2755" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2755"/>
+  <dimension ref="A1:E2756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74813,6 +74813,33 @@
         </is>
       </c>
     </row>
+    <row r="2756">
+      <c r="A2756" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B2756" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2756" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D2756" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E2756" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2756"/>
+  <dimension ref="A1:E2757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74840,6 +74840,33 @@
         </is>
       </c>
     </row>
+    <row r="2757">
+      <c r="A2757" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B2757" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2757" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D2757" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E2757" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2757"/>
+  <dimension ref="A1:E2758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74867,6 +74867,33 @@
         </is>
       </c>
     </row>
+    <row r="2758">
+      <c r="A2758" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B2758" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2758" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D2758" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E2758" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2758"/>
+  <dimension ref="A1:E2759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74894,6 +74894,33 @@
         </is>
       </c>
     </row>
+    <row r="2759">
+      <c r="A2759" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2759" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2759" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D2759" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E2759" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2759"/>
+  <dimension ref="A1:E2760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74921,6 +74921,33 @@
         </is>
       </c>
     </row>
+    <row r="2760">
+      <c r="A2760" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2760" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2760" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D2760" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E2760" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2760"/>
+  <dimension ref="A1:E2761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74948,6 +74948,33 @@
         </is>
       </c>
     </row>
+    <row r="2761">
+      <c r="A2761" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2761" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2761" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D2761" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E2761" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2761"/>
+  <dimension ref="A1:E2762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74975,6 +74975,33 @@
         </is>
       </c>
     </row>
+    <row r="2762">
+      <c r="A2762" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2762" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2762" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D2762" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E2762" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2762"/>
+  <dimension ref="A1:E2763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75002,6 +75002,33 @@
         </is>
       </c>
     </row>
+    <row r="2763">
+      <c r="A2763" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2763" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2763" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D2763" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E2763" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2763"/>
+  <dimension ref="A1:E2764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75029,6 +75029,33 @@
         </is>
       </c>
     </row>
+    <row r="2764">
+      <c r="A2764" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2764" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2764" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D2764" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E2764" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2764"/>
+  <dimension ref="A1:E2765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75056,6 +75056,33 @@
         </is>
       </c>
     </row>
+    <row r="2765">
+      <c r="A2765" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2765" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2765" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D2765" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E2765" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2765"/>
+  <dimension ref="A1:E2766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75083,6 +75083,33 @@
         </is>
       </c>
     </row>
+    <row r="2766">
+      <c r="A2766" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2766" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2766" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D2766" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E2766" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2766"/>
+  <dimension ref="A1:E2767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75110,6 +75110,33 @@
         </is>
       </c>
     </row>
+    <row r="2767">
+      <c r="A2767" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2767" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2767" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D2767" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E2767" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2767"/>
+  <dimension ref="A1:E2769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75137,6 +75137,60 @@
         </is>
       </c>
     </row>
+    <row r="2768">
+      <c r="A2768" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2768" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2768" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D2768" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E2768" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="2769">
+      <c r="A2769" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B2769" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2769" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D2769" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E2769" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
